--- a/Data/Config.xlsxtemp.xlsx
+++ b/Data/Config.xlsxtemp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_SignedInvoicePDFClassification_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C86E24D-50ED-41E1-9AA4-EE53F28577F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CF33A8-6304-4CBA-9120-B993BA4EDE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4605" yWindow="975" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>Name</t>
   </si>
@@ -101,10 +101,6 @@
   </si>
   <si>
     <t>Framework</t>
-  </si>
-  <si>
-    <t>Orchestrator queue Name. The value must match with the queue name defined on Orchestrator.</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Logging field which allows grouping of log data of two or more subprocesses under the same business process name</t>
@@ -129,9 +125,6 @@
     <t>OrchestratorAssetFolder</t>
   </si>
   <si>
-    <t>Folder name. The value must match a folder defined in Orchestrator and queue specified as OrchestratorQueueName should be created in this folder. For classic folders leave the value field empty.</t>
-  </si>
-  <si>
     <t>MaxConsecutiveSystemExceptions</t>
   </si>
   <si>
@@ -165,27 +158,15 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>use in Main-&gt; Initialization</t>
-  </si>
-  <si>
-    <t>Supported Datetime format of Now.ToString</t>
-  </si>
-  <si>
     <t>RetryNumberAddTransactionItem</t>
   </si>
   <si>
-    <t>FilePath</t>
-  </si>
-  <si>
     <t>Non Production/UCL/UCL_SignedInvoiceStoring</t>
   </si>
   <si>
     <t>LogMessage_TryToGetNewLocalFile</t>
   </si>
   <si>
-    <t>ddMMyyyy_HHmmss</t>
-  </si>
-  <si>
     <t>Try to get new local file.</t>
   </si>
   <si>
@@ -195,227 +176,66 @@
     <t>UCLPMS_ConnectionString</t>
   </si>
   <si>
-    <t>strInvoiceValidStatus</t>
-  </si>
-  <si>
-    <t>log_validInvoiceProcessing</t>
-  </si>
-  <si>
-    <t>Processing Valid-Invoice ID:</t>
-  </si>
-  <si>
-    <t>Bookmark: Log Message log_validInvoiceProcessing</t>
-  </si>
-  <si>
-    <t>logE_UnexpectedDiverseKey</t>
-  </si>
-  <si>
-    <t>Unexpected dictInvoiceFileSetForInsert/currentKeyValuePairOfTextAndDataRow diverse key.</t>
-  </si>
-  <si>
-    <t>Bookmark: Throw logE_UnexpectedDiverseKey</t>
-  </si>
-  <si>
-    <t>strQueryUploadInvoice</t>
-  </si>
-  <si>
-    <t>logE_UnexpectedQueryResult</t>
-  </si>
-  <si>
-    <t>The updated file to SQL Server was not affected, Invoice No. @INVOICE_NO, Invoice ID @INVOICE_ID</t>
-  </si>
-  <si>
-    <t>Bookmark: Throw logE_UnexpectedQueryResult
-Parameter:
-@INVOICE_ID
-@INVOICE_NO</t>
-  </si>
-  <si>
-    <t>Update Successfully</t>
-  </si>
-  <si>
-    <t>log_successfullyUpdatedToSQL</t>
-  </si>
-  <si>
-    <t>Bookmark: Log Message log_successfullyUpdatedToSQL</t>
-  </si>
-  <si>
-    <t>strRawFilesFolderPath</t>
-  </si>
-  <si>
-    <t>strFinishProcessedFilesFolderPath</t>
-  </si>
-  <si>
-    <t>AWaiting for Approval</t>
-  </si>
-  <si>
-    <t>Bookmark: Run Query Upload Invoice
-Query Parameters:
-$IN_INVOICE_ID$ = INVOICE_ID of the invoice.
-$IN_BASE64$ = converted base64 of the invoice file.
-Required output:
-RESULT_CODE
-RESULT_MESSAGES</t>
-  </si>
-  <si>
-    <t>declare @ResultCode nvarchar(10)
-	,@ResultMessages NVARCHAR(MAX)
-EXECUTE [dbo].[UPLOAD_AND_UPDATE_APPROVED_INVOICE] 
-   @INVOICE_ID = '$IN_INVOICE_ID$'
-  ,@BASE64 = '$IN_BASE64$'
-  ,@ResultCode = @ResultCode OUTPUT
-  ,@ResultMessages = @ResultMessages OUTPUT
-SELECT @ResultCode AS RESULT_CODE , @ResultMessages as RESULT_MESSAGES</t>
-  </si>
-  <si>
-    <t>StorageFilePath</t>
-  </si>
-  <si>
-    <t>strSearchingPatternTableColumnName_RegEx</t>
-  </si>
-  <si>
-    <t>RegEx</t>
-  </si>
-  <si>
-    <t>strSearchingPatternTableColumnName_Enable</t>
-  </si>
-  <si>
-    <t>Enable</t>
-  </si>
-  <si>
     <t>RetryNumberUploadStorageItem</t>
   </si>
   <si>
     <t>RetryNumberDeleteStorageItem</t>
   </si>
   <si>
-    <t>Raw_PDF_Page</t>
-  </si>
-  <si>
-    <t>OrchestratorQueueName_PDF_Dispatcher</t>
-  </si>
-  <si>
-    <t>OrchestratorQueueFolder_PDF_Dispatcher</t>
-  </si>
-  <si>
-    <t>strTransactionReferenceFormat_PDF_Dispatcher</t>
-  </si>
-  <si>
-    <t>strTransactionReferencePageFormat_PDF_Dispatcher</t>
-  </si>
-  <si>
-    <t>$TransactionReference$_$FileName$_P$PageIndex$</t>
-  </si>
-  <si>
-    <t>Supported parameter:
-$TransactionReference$ = strTransactionReferenceFormat_PDF_Dispatcher
-$FileName$ = Master file name
-$PageIndex$ = Page number</t>
-  </si>
-  <si>
-    <t>strStorageBucketName_PDF_Dispatcher</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_MoveToPath</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_StorageFileName</t>
-  </si>
-  <si>
-    <t>MasterFile_MoveTo</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_MasterFilePath</t>
-  </si>
-  <si>
-    <t>strStorageBucketFolder_PDF_Dispatcher</t>
-  </si>
-  <si>
-    <t>InvoiceNumberFound</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_InvoiceNumberFound</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_INVOICE_ID</t>
-  </si>
-  <si>
-    <t>INVOICE_ID</t>
-  </si>
-  <si>
-    <t>C:\Users\BARA\Documents\UCL</t>
-  </si>
-  <si>
-    <t>C:\Users\BARA\Documents\UCL_F</t>
-  </si>
-  <si>
-    <t>InvoiceForReport</t>
-  </si>
-  <si>
-    <t>OrchestratorQueueName_Report</t>
-  </si>
-  <si>
-    <t>OrchestratorQueueFolder_Report</t>
-  </si>
-  <si>
-    <t>strReport_TransactionDetailKey_INVOICE_NO</t>
-  </si>
-  <si>
-    <t>strReport_TransactionDetailKey_InvoiceDate</t>
-  </si>
-  <si>
-    <t>INVOICE_NO</t>
-  </si>
-  <si>
-    <t>Customer Name</t>
-  </si>
-  <si>
-    <t>Invoice Date</t>
-  </si>
-  <si>
-    <t>strReport_TransactionDetailKey_CustomerName</t>
-  </si>
-  <si>
-    <t>strQueryGetInvoiceDetail</t>
-  </si>
-  <si>
-    <t>Bookmark: Run Query Upload Invoice
-Query Parameters:
-$IN_INVOICE_NO$ = INVOICE_NO of the invoice.</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_COMPANY_NAME</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_INVOICE_DATE</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_STATUS</t>
-  </si>
-  <si>
-    <t>Invoice Status</t>
-  </si>
-  <si>
-    <t>strRawPDFPage_TransactionDetailKey_INVOICE_NO</t>
-  </si>
-  <si>
-    <t>strReport_TemplateDocPath</t>
-  </si>
-  <si>
-    <t>Data/UPL_summary_report.docx</t>
-  </si>
-  <si>
-    <t>SELECT TOP 1 invoice.INVOICE_NO, invoice.INVOICE_ID, invoice.STATUS, PDFFile.PDF_INVOICE_DRAFT_FILE,
-invoice.COMPANY_NAME,
-FORMAT(invoice.CREATE_DATE, 'dd/MM/yyyy') as CREATE_DATE
-		FROM dbo.PMS_INVOICE_QAS invoice
-		LEFT JOIN PMS_INVOICE_FILE PDFFile on invoice.INVOICE_ID = PDFFile.INVOICE_ID
-		WHERE 
-		(invoice.INVOICE_NO = '$IN_INVOICE_NO$')
-		AND (invoice.DELETE_FLAG = 0)</t>
+    <t>strSelectQuery</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>int_RDE_DayOfExpire</t>
+  </si>
+  <si>
+    <t>RDE_strDayOfExpire</t>
+  </si>
+  <si>
+    <t>Parameter
+$OFFSET$ = days before they expired to notify.</t>
+  </si>
+  <si>
+    <t>SELECT DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) as DAYS_UNTIL_END 
+,profile.COMPANY_PROFILE_PERIOD_END
+,CASE company.COMPANY_LANGUAGE_TYPE WHEN 'EN' THEN company.COMPANY_NAME_EN ELSE
+company.COMPANY_NAME_TH END AS COMPANY_NAME
+,invent.INVENTORY_NAME
+,profile.COMPANY_PROFILE_AGREEMENT_NO
+FROM PMS_COMPANY_PROFILE_LM profile
+left join PMS_PRODUCT_INVENTORY_LM invent on [profile].INVENTORY_ID = invent.INVENTORY_ID AND invent.DELETE_FLAG = 0
+left join PMS_COMPANY_LM company on [profile].COMPANY_ID = company.COMPANY_ID AND company.DELETE_FLAG = 0
+  WHERE [profile].DELETE_FLAG = 0 AND (RENEW_ID is NULL OR RENEW_ID = '')
+AND COMPANY_PROFILE_PERIOD_END IS NOT NULL
+AND DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) &lt;= $OFFSET$
+AND (COMPANY_NAME_TH &lt;&gt; N'UCL ZERO' or COMPANY_NAME_EN &lt;&gt; N'UCL ZERO')
+ORDER BY profile.COMPANY_PROFILE_PERIOD_END ASC</t>
+  </si>
+  <si>
+    <t>strTemplatePath_Reminder_Expire</t>
+  </si>
+  <si>
+    <t>strTemplatePath_Reminder_Expire_Not_found</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire.docx</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire_Not_found.docx</t>
+  </si>
+  <si>
+    <t>Data\Output</t>
+  </si>
+  <si>
+    <t>strProcessedResourceFilePath</t>
+  </si>
+  <si>
+    <t>strTemplateReplaceString_ExpireDataTable</t>
+  </si>
+  <si>
+    <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
   </si>
 </sst>
 </file>
@@ -447,24 +267,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -479,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -501,27 +309,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -836,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1006"/>
+  <dimension ref="A1:Z977"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="58.140625" style="4" customWidth="1"/>
@@ -881,345 +668,124 @@
       <c r="Z1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
-      <c r="A3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>30</v>
+    <row r="4" spans="1:26">
+      <c r="A4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4">
+        <v>60</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>43</v>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="60">
-      <c r="A5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>84</v>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="10"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="10"/>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>42</v>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="11"/>
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="13"/>
+    <row r="10" spans="1:26" ht="409.5">
+      <c r="A10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="13"/>
-    </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="11"/>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="11"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="11"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="11"/>
-    </row>
-    <row r="19" spans="1:3" s="15" customFormat="1">
-      <c r="A19" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="15" customFormat="1">
-      <c r="A20" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="15" customFormat="1">
-      <c r="A21" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="15" customFormat="1">
-      <c r="A22" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="15" customFormat="1">
-      <c r="A23" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="15" customFormat="1">
-      <c r="A24" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3"/>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="180">
-      <c r="A37" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="195">
-      <c r="A38" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -2149,35 +1715,6 @@
     <row r="975" ht="14.25" customHeight="1"/>
     <row r="976" ht="14.25" customHeight="1"/>
     <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
-    <row r="1001" ht="14.25" customHeight="1"/>
-    <row r="1002" ht="14.25" customHeight="1"/>
-    <row r="1003" ht="14.25" customHeight="1"/>
-    <row r="1004" ht="14.25" customHeight="1"/>
-    <row r="1005" ht="14.25" customHeight="1"/>
-    <row r="1006" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2238,18 +1775,18 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2273,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -2295,7 +1832,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
@@ -2306,15 +1843,15 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
@@ -2325,46 +1862,46 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -2372,7 +1909,7 @@
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -2380,7 +1917,7 @@
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -2388,13 +1925,13 @@
     </row>
     <row r="20" spans="1:3" ht="45">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B20" t="b">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3393,7 +2930,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -3421,7 +2958,17 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsxtemp.xlsx
+++ b/Data/Config.xlsxtemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_Remider_Expire\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CF33A8-6304-4CBA-9120-B993BA4EDE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A45171-7DEA-4E61-9C30-3D3B497D8839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
   <si>
     <t>Name</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Description (Assets will always overwrite other config)</t>
-  </si>
-  <si>
-    <t>MaxRetryNumber</t>
   </si>
   <si>
     <t>ExScreenshotsFolderPath</t>
@@ -107,9 +104,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
-  </si>
-  <si>
     <t>Static part of logging message. Processed Transaction succesful.</t>
   </si>
   <si>
@@ -198,8 +192,80 @@
 $OFFSET$ = days before they expired to notify.</t>
   </si>
   <si>
+    <t>strTemplatePath_Reminder_Expire</t>
+  </si>
+  <si>
+    <t>strTemplatePath_Reminder_Expire_Not_found</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire.docx</t>
+  </si>
+  <si>
+    <t>Data\Temp\Reminder_Expire_Not_found.docx</t>
+  </si>
+  <si>
+    <t>Data\Output</t>
+  </si>
+  <si>
+    <t>strProcessedResourceFilePath</t>
+  </si>
+  <si>
+    <t>strTemplateReplaceString_ExpireDataTable</t>
+  </si>
+  <si>
+    <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
+  </si>
+  <si>
+    <t>strMailSubject_Report</t>
+  </si>
+  <si>
+    <t>strMailSubject_NoReport</t>
+  </si>
+  <si>
+    <t>Test Report</t>
+  </si>
+  <si>
+    <t>Test Not found</t>
+  </si>
+  <si>
+    <t>strMailSendTo</t>
+  </si>
+  <si>
+    <t>Aphiruth.s@baraadv.co.th</t>
+  </si>
+  <si>
+    <t>strMailSubject_SystemError</t>
+  </si>
+  <si>
+    <t>strMailSubject_BusinessError</t>
+  </si>
+  <si>
+    <t>strMailSendTo_SystemError</t>
+  </si>
+  <si>
+    <t>strMailSendTo_BusinessError</t>
+  </si>
+  <si>
+    <t>Multiple email split by comma (,)</t>
+  </si>
+  <si>
+    <t>Expired Profile Reminder Prosess Error</t>
+  </si>
+  <si>
+    <t>Aphiruth.s@baraadv.co.th,korakrit.s@baraadv.co.th,</t>
+  </si>
+  <si>
+    <t>Expired Profile Reminder Prosess Business Error</t>
+  </si>
+  <si>
+    <t>_TEMP</t>
+  </si>
+  <si>
+    <t>strTemplateKeySubfix</t>
+  </si>
+  <si>
     <t>SELECT DATEDIFF(DAY, CAST(GETDATE() AS DATE), CAST(COMPANY_PROFILE_PERIOD_END AS DATE)) as DAYS_UNTIL_END 
-,profile.COMPANY_PROFILE_PERIOD_END
+,FORMAT( profile.COMPANY_PROFILE_PERIOD_END,'d MMM yyyy') AS COMPANY_PROFILE_PERIOD_END
 ,CASE company.COMPANY_LANGUAGE_TYPE WHEN 'EN' THEN company.COMPANY_NAME_EN ELSE
 company.COMPANY_NAME_TH END AS COMPANY_NAME
 ,invent.INVENTORY_NAME
@@ -214,35 +280,37 @@
 ORDER BY profile.COMPANY_PROFILE_PERIOD_END ASC</t>
   </si>
   <si>
-    <t>strTemplatePath_Reminder_Expire</t>
-  </si>
-  <si>
-    <t>strTemplatePath_Reminder_Expire_Not_found</t>
-  </si>
-  <si>
-    <t>Data\Temp\Reminder_Expire.docx</t>
-  </si>
-  <si>
-    <t>Data\Temp\Reminder_Expire_Not_found.docx</t>
-  </si>
-  <si>
-    <t>Data\Output</t>
-  </si>
-  <si>
-    <t>strProcessedResourceFilePath</t>
-  </si>
-  <si>
-    <t>strTemplateReplaceString_ExpireDataTable</t>
-  </si>
-  <si>
-    <t>&lt;$RDE_dt_Reminder_Expire_Report$&gt;</t>
+    <t>strMailTableStyle</t>
+  </si>
+  <si>
+    <t>table {
+width: 100%;
+border-collapse: separate;
+border-spacing: 0;
+border: 1px solid #999;
+border-radius: 5px;
+overflow: hidden;
+}
+th {
+font-weight: bold;
+text-align: center;
+padding: 8px;
+background-color: #f2f2f2;
+border: 1px solid #ddd;
+}
+td {
+text-align: center;
+padding: 8px;
+border: 1px solid #ddd;
+align-content: start;
+}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -266,6 +334,17 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -284,10 +363,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -309,8 +389,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -623,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z977"/>
+  <dimension ref="A1:Z986"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="58.140625" style="4" customWidth="1"/>
@@ -669,107 +756,179 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="5" spans="1:26">
+      <c r="A5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="4">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>45</v>
+      <c r="C5" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>58</v>
+      <c r="B11" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="409.5">
-      <c r="A10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>52</v>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="315">
+      <c r="A18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="409.5">
+      <c r="A19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -1715,16 +1874,30 @@
     <row r="975" ht="14.25" customHeight="1"/>
     <row r="976" ht="14.25" customHeight="1"/>
     <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B13" r:id="rId1" xr:uid="{F0564C91-B156-493F-A907-F75E6406DBB7}"/>
+    <hyperlink ref="B16" r:id="rId2" xr:uid="{1CB6BA4B-5780-47B7-8EAD-3BF281ED260F}"/>
+    <hyperlink ref="B17" r:id="rId3" xr:uid="{9089DD37-D27C-43DB-96D8-363F3C3D3DC7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z991"/>
+  <dimension ref="A1:Z990"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1767,173 +1940,163 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="45">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>37</v>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
-        <v>40</v>
+      <c r="A17" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A18" s="8" t="s">
-        <v>46</v>
+      <c r="A18" t="s">
+        <v>45</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+    <row r="19" spans="1:3" ht="45">
       <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="B19" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2904,7 +3067,6 @@
     <row r="988" ht="14.25" customHeight="1"/>
     <row r="989" ht="14.25" customHeight="1"/>
     <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2930,7 +3092,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -2960,17 +3122,21 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" s="4"/>
+    </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
